--- a/hardware/hot-info-orbs-xiao/bom/hot_info_orbs_xiao_bom.xlsx
+++ b/hardware/hot-info-orbs-xiao/bom/hot_info_orbs_xiao_bom.xlsx
@@ -10,7 +10,7 @@
     <sheet name="BOM" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'BOM'!$A$1:$J$12</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'BOM'!$A$1:$J$13</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -445,7 +445,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J12"/>
+  <dimension ref="A1:J13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -551,12 +551,12 @@
       </c>
       <c r="I2" s="3" t="inlineStr">
         <is>
-          <t>https://thepihut.com/products/seeed-xiao-esp32s3-plus</t>
+          <t>https://www.amazon.com/dp/B0H6XJGN3Z</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>Plus boards ship WITHOUT pin headers: see the header and socket lines below. Mounted on the back, on sockets.</t>
+          <t>Plus boards ship WITHOUT pin headers: see the header and socket lines below. Mounted on the back, on sockets. The plain XIAO ESP32-S3 (https://www.amazon.com/dp/B0BYSB66S5) is interchangeable and runs the same 8 MB binary. AliExpress: https://www.aliexpress.us/item/3256808599305867.html</t>
         </is>
       </c>
     </row>
@@ -594,61 +594,61 @@
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/MTDELE-Display-Compatible-Arduino-Interfac/dp/B0DJ13VW73</t>
+          <t>https://www.amazon.com/dp/B0DJ13VW73</t>
         </is>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/AITRIP-1-28-Display-Multicolored-Arduino/dp/B0H6RQ4C54</t>
+          <t>https://www.aliexpress.us/item/3256813175276825.html</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>Check the listing's pin order before buying; the footprint is pad 1 = VCC (+5V) .. pad 7 = RST. The module's own male header plugs into the female socket below.</t>
+          <t>Check the listing's pin order before buying; the footprint is pad 1 = VCC (+5V) .. pad 7 = RST. The module's own male header plugs into the female socket below. Lit area ~32.5 mm dia (docs/DISPLAY-EDGE-TEST.md).</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="n">
+      <c r="A4" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>J (displays)</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="n">
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>LENS1-LENS5</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>Female socket 1x07, 2.54 mm, straight</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>8.5 mm body, through hole</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>PinSocket_1x07_P2.54mm_Vertical (in GC9A01_SOCKET)</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>Sullins PPTC071LFBN-RC</t>
-        </is>
-      </c>
-      <c r="H4" s="3" t="inlineStr">
-        <is>
-          <t>https://www.digikey.com/en/products/detail/sullins-connector-solutions/PPTC071LFBN-RC/810146</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr"/>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>Not a schematic part: modeled inside the display footprint. 8.5 mm is the lift the 3D assumes.</t>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>Display lens: mineral watch crystal, double dome</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>2.0 mm thick; DIAMETER NOT CHOSEN (26-45 mm offered)</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>enclosure part, no footprint</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>generic</t>
+        </is>
+      </c>
+      <c r="H4" s="5" t="inlineStr">
+        <is>
+          <t>https://www.aliexpress.us/item/3256806569387664.html</t>
+        </is>
+      </c>
+      <c r="I4" s="4" t="inlineStr"/>
+      <c r="J4" s="4" t="inlineStr">
+        <is>
+          <t>Diameter is set by the enclosure bezel, not chosen yet; must clear the ~32.5 mm lit area. Pick the size option on the listing. No Amazon source found yet.</t>
         </is>
       </c>
     </row>
@@ -658,11 +658,11 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>J (XIAO)</t>
+          <t>J (displays)</t>
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -676,23 +676,27 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>in XIAO-ESP32-S3-SOCKET</t>
+          <t>PinSocket_1x07_P2.54mm_Vertical (in GC9A01_SOCKET)</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>Sullins PPTC071LFBN-RC</t>
+          <t>Sullins PPTC071LFBN-RC (reference)</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>https://www.digikey.com/en/products/detail/sullins-connector-solutions/PPTC071LFBN-RC/810146</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr"/>
+          <t>https://www.amazon.com/dp/B0GM7T6XWP</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>https://www.aliexpress.us/item/3256812879331298.html</t>
+        </is>
+      </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>Same part as the display sockets; 7 per board in all.</t>
+          <t>Not a schematic part: modeled inside the display footprint. 8.5 mm is the lift the 3D assumes; the marketplace sockets' body height is NOT verified. On AliExpress choose the 7P option.</t>
         </is>
       </c>
     </row>
@@ -702,7 +706,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>P (XIAO)</t>
+          <t>J (XIAO)</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
@@ -710,12 +714,12 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Male header 1x07, 2.54 mm</t>
+          <t>Female socket 1x07, 2.54 mm, straight</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>cut from a 1x40 breakaway strip (1 strip = 5 sets)</t>
+          <t>8.5 mm body, through hole</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -725,18 +729,22 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>Sullins PRPC040SAAN-RC</t>
+          <t>Sullins PPTC071LFBN-RC (reference)</t>
         </is>
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t>https://www.digikey.com/en/products/detail/sullins-connector-solutions/PRPC040SAAN-RC/2775214</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr"/>
+          <t>https://www.amazon.com/dp/B0GM7T6XWP</t>
+        </is>
+      </c>
+      <c r="I6" s="3" t="inlineStr">
+        <is>
+          <t>https://www.aliexpress.us/item/3256812879331298.html</t>
+        </is>
+      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>Soldered to the XIAO, plugs into the XIAO sockets.</t>
+          <t>Same part as the display sockets; 7 per board in all.</t>
         </is>
       </c>
     </row>
@@ -746,45 +754,45 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>SW1-SW3</t>
+          <t>P (XIAO)</t>
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Tactile switch, right angle, 6x6 mm</t>
+          <t>Male header 1x07, 2.54 mm</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>SPST-NO, through hole, side actuated</t>
+          <t>cut from a 1x40 breakaway strip (1 strip = 5 sets)</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>SW_Tactile_SPST_Angled_PTS645Vx39-2LFS</t>
+          <t>in XIAO-ESP32-S3-SOCKET</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>C&amp;K PTS645VL39-2 LFS</t>
+          <t>Sullins PRPC040SAAN-RC (reference)</t>
         </is>
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t>https://www.digikey.com/en/products/detail/c-k/PTS645VL39-2-LFS/1146765</t>
+          <t>https://www.amazon.com/dp/B0FRZW75VS</t>
         </is>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>https://lcsc.com/product-detail/Tactile-Switches_C-K-PTS645VL392LFS_C285523.html</t>
+          <t>https://www.aliexpress.us/item/3256806779943089.html</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>Footprint is the C&amp;K part. The uxcell 6x6x8 right-angle switches in the README are NOT verified to fit this footprint.</t>
+          <t>Soldered to the XIAO, plugs into the XIAO sockets.</t>
         </is>
       </c>
     </row>
@@ -794,93 +802,93 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
+          <t>SW1-SW3</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>Tactile switch, right angle, 6x6 mm</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>SPST-NO, through hole, side actuated</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>SW_Tactile_SPST_Angled_PTS645Vx39-2LFS</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="inlineStr">
+        <is>
+          <t>C&amp;K PTS645VL39-2 LFS (footprint part)</t>
+        </is>
+      </c>
+      <c r="H8" s="5" t="inlineStr">
+        <is>
+          <t>https://www.amazon.com/dp/B008DS13P2</t>
+        </is>
+      </c>
+      <c r="I8" s="5" t="inlineStr">
+        <is>
+          <t>https://www.aliexpress.us/item/3256810140983087.html</t>
+        </is>
+      </c>
+      <c r="J8" s="4" t="inlineStr">
+        <is>
+          <t>FIT NOT VERIFIED: the footprint is the C&amp;K part (7.0 mm mounting-pin pitch); the uxcell 6x6x8 on Amazon lists 6.5 mm. Check one against the board before buying a lot. Exact part: https://lcsc.com/product-detail/Tactile-Switches_C-K-PTS645VL392LFS_C285523.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
           <t>C1</t>
         </is>
       </c>
-      <c r="C8" s="4" t="n">
+      <c r="C9" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="D8" s="4" t="inlineStr">
+      <c r="D9" s="4" t="inlineStr">
         <is>
           <t>Electrolytic capacitor, +5V bulk</t>
         </is>
       </c>
-      <c r="E8" s="4" t="inlineStr">
+      <c r="E9" s="4" t="inlineStr">
         <is>
           <t>VALUE NOT IN SCHEMATIC - suggested 100 uF 16 V, 6.3 mm dia, 2.5 mm pitch</t>
         </is>
       </c>
-      <c r="F8" s="4" t="inlineStr">
+      <c r="F9" s="4" t="inlineStr">
         <is>
           <t>CP_Radial_D6.3mm_P2.50mm</t>
         </is>
       </c>
-      <c r="G8" s="4" t="inlineStr">
+      <c r="G9" s="4" t="inlineStr">
         <is>
           <t>Panasonic EEU-FC1C101H (suggested)</t>
         </is>
       </c>
-      <c r="H8" s="5" t="inlineStr">
-        <is>
-          <t>https://www.digikey.com/en/products/detail/panasonic-electronic-components/EEU-FC1C101H/2689573</t>
-        </is>
-      </c>
-      <c r="I8" s="5" t="inlineStr">
-        <is>
-          <t>https://www.digikey.com/en/products/detail/panasonic-electronic-components/EEU-FC1C101/356102</t>
-        </is>
-      </c>
-      <c r="J8" s="4" t="inlineStr">
-        <is>
-          <t>Schematic Value field holds the symbol name only - pick and record a value. EEU-FC1C101H is 12.2 mm tall on the back side; check enclosure clearance.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>C2</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>Ceramic capacitor 1 uF</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>50 V X7R, radial, 5.08 mm lead spacing</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>C_Disc_D5.0mm_W2.5mm_P5.00mm</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>KEMET C330C105K5R5TA7301</t>
-        </is>
-      </c>
-      <c r="H9" s="3" t="inlineStr">
-        <is>
-          <t>https://www.digikey.com/en/products/detail/kemet/C330C105K5R5TA7301/399-9886-1-ND/3726180</t>
-        </is>
-      </c>
-      <c r="I9" s="3" t="inlineStr">
-        <is>
-          <t>https://www.digikey.com/en/products/detail/kyocera-avx/SE015C105KAR/2060741</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>Display RST hold-off with R1.</t>
+      <c r="H9" s="5" t="inlineStr">
+        <is>
+          <t>https://www.amazon.com/dp/B0CPDF3HHB</t>
+        </is>
+      </c>
+      <c r="I9" s="5" t="inlineStr">
+        <is>
+          <t>https://www.aliexpress.us/item/3256812824344961.html</t>
+        </is>
+      </c>
+      <c r="J9" s="4" t="inlineStr">
+        <is>
+          <t>Schematic Value field holds the symbol name only - pick and record a value. The Amazon kit lists no dimensions: check 6.3 mm dia / 2.5 mm pitch. AliExpress is Nichicon 6.3x7. Height is on the back side; check enclosure clearance.</t>
         </is>
       </c>
     </row>
@@ -890,7 +898,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>C2</t>
         </is>
       </c>
       <c r="C10" s="2" t="n">
@@ -898,37 +906,37 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Resistor 10k</t>
+          <t>Ceramic capacitor 1 uF (105)</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1/4 W 5 % carbon film, axial, 10.16 mm pitch</t>
+          <t>50 V, radial, 5.08 mm lead spacing</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>R_Axial_DIN0207_L6.3mm_D2.5mm_P10.16mm_Horizontal</t>
+          <t>C_Disc_D5.0mm_W2.5mm_P5.00mm</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>Stackpole CF14JT10K0</t>
+          <t>KEMET C330C105K5R5TA7301 (reference)</t>
         </is>
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t>https://www.digikey.com/en/products/detail/stackpole-electronics-inc/CF14JT10K0/1741265</t>
+          <t>https://www.amazon.com/dp/B08BF91KY3</t>
         </is>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>https://www.digikey.com/en/products/detail/stackpole-electronics-inc/CFM14JT10K0/1742061</t>
+          <t>https://www.aliexpress.us/item/3256811560978404.html</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>Display RST pull-up to 3V3.</t>
+          <t>Display RST hold-off with R1. Both listings are 5.08 mm pitch.</t>
         </is>
       </c>
     </row>
@@ -938,41 +946,45 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>H1-H7</t>
+          <t>R1</t>
         </is>
       </c>
       <c r="C11" s="2" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>M3 screw (mounting)</t>
+          <t>Resistor 10k</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>M3-0.5, socket head; 3.2 mm holes</t>
+          <t>1/4 W 5 % carbon film, axial, 10.16 mm pitch</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>Edge.Cuts circles, no footprint</t>
+          <t>R_Axial_DIN0207_L6.3mm_D2.5mm_P10.16mm_Horizontal</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>M3 x 6 DIN 912 (length depends on the enclosure)</t>
+          <t>Stackpole CF14JT10K0 (reference)</t>
         </is>
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t>https://www.aspenfasteners.com/m3-0-5-x-6mm-din-912-iso-4762-metric-socket-head-cap-screws-hex-socket-drive-class-12-9-steel-plain-unbrako/</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr"/>
+          <t>https://www.amazon.com/dp/B0CL9KXXZB</t>
+        </is>
+      </c>
+      <c r="I11" s="3" t="inlineStr">
+        <is>
+          <t>https://www.aliexpress.us/item/3256807898146236.html</t>
+        </is>
+      </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>Standoffs/length set by the enclosure, not chosen yet.</t>
+          <t>Display RST pull-up to 3V3.</t>
         </is>
       </c>
     </row>
@@ -982,50 +994,98 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
+          <t>H1-H7</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>M3 screw (mounting)</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>M3-0.5, socket head; 3.2 mm holes</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>Edge.Cuts circles, no footprint</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>M3 x 6 DIN 912 class 12.9 (length depends on the enclosure)</t>
+        </is>
+      </c>
+      <c r="H12" s="3" t="inlineStr">
+        <is>
+          <t>https://www.amazon.com/dp/B0DJQH3WSX</t>
+        </is>
+      </c>
+      <c r="I12" s="3" t="inlineStr">
+        <is>
+          <t>https://www.aliexpress.us/item/3256805704775238.html</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>Standoffs/length set by the enclosure, not chosen yet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
           <t>PCB</t>
         </is>
       </c>
-      <c r="C12" s="2" t="n">
+      <c r="C13" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="D13" s="2" t="inlineStr">
         <is>
           <t>Bare board</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="E13" s="2" t="inlineStr">
         <is>
           <t>2 layer, 1.6 mm, 198.82 x 47.78 mm, WHITE solder mask, BLACK silkscreen</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="F13" s="2" t="inlineStr">
         <is>
           <t>hot_info_orbs_xiao.kicad_pcb</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H12" s="3" t="inlineStr">
+      <c r="H13" s="3" t="inlineStr">
         <is>
           <t>https://jlcpcb.com/quote/pcbOrderFaq/PCB%20Color</t>
         </is>
       </c>
-      <c r="I12" s="3" t="inlineStr">
+      <c r="I13" s="3" t="inlineStr">
         <is>
           <t>https://www.pcbway.com/</t>
         </is>
       </c>
-      <c r="J12" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>Order the colors explicitly: the stackup colors only drive the 3D/STEP, not the gerbers.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J12"/>
+  <autoFilter ref="A1:J13"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I2" r:id="rId2"/>
@@ -1033,18 +1093,23 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I3" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H4" r:id="rId5"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H5" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H6" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H7" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I7" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H8" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I8" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H9" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I9" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H10" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I10" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H11" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H12" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I12" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I5" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H6" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I6" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H7" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I7" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H8" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I8" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H9" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I9" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H10" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I10" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H11" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I11" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H12" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I12" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H13" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I13" r:id="rId23"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/hardware/hot-info-orbs-xiao/bom/hot_info_orbs_xiao_bom.xlsx
+++ b/hardware/hot-info-orbs-xiao/bom/hot_info_orbs_xiao_bom.xlsx
@@ -609,46 +609,46 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="n">
+      <c r="A4" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="4" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>LENS1-LENS5</t>
         </is>
       </c>
-      <c r="C4" s="4" t="n">
+      <c r="C4" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="D4" s="4" t="inlineStr">
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>Display lens: mineral watch crystal, double dome</t>
         </is>
       </c>
-      <c r="E4" s="4" t="inlineStr">
-        <is>
-          <t>2.0 mm thick; DIAMETER NOT CHOSEN (26-45 mm offered)</t>
-        </is>
-      </c>
-      <c r="F4" s="4" t="inlineStr">
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>35.5 mm dia, 2.0 mm thick</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>enclosure part, no footprint</t>
         </is>
       </c>
-      <c r="G4" s="4" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>generic</t>
         </is>
       </c>
-      <c r="H4" s="5" t="inlineStr">
+      <c r="H4" s="3" t="inlineStr">
         <is>
           <t>https://www.aliexpress.us/item/3256806569387664.html</t>
         </is>
       </c>
-      <c r="I4" s="4" t="inlineStr"/>
-      <c r="J4" s="4" t="inlineStr">
-        <is>
-          <t>Diameter is set by the enclosure bezel, not chosen yet; must clear the ~32.5 mm lit area. Pick the size option on the listing. No Amazon source found yet.</t>
+      <c r="I4" s="2" t="inlineStr"/>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>Choose the Diameter 35.5mm option on the listing (Scott, 2026-10-17); clears the ~32.5 mm lit area. No Amazon source found yet.</t>
         </is>
       </c>
     </row>

--- a/hardware/hot-info-orbs-xiao/bom/hot_info_orbs_xiao_bom.xlsx
+++ b/hardware/hot-info-orbs-xiao/bom/hot_info_orbs_xiao_bom.xlsx
@@ -526,12 +526,12 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Seeed Studio XIAO ESP32-S3 Plus</t>
+          <t>Seeed Studio XIAO ESP32-S3</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>ESP32-S3R8, 16 MB flash, 8 MB PSRAM; SKU 102010671</t>
+          <t>ESP32-S3R8, 8 MB flash, 8 MB PSRAM; SKU 113991114</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -541,22 +541,22 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>102010671</t>
+          <t>113991114</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
-          <t>https://www.seeedstudio.com/Seeed-Studio-XIAO-ESP32S3-Plus-p-6361.html</t>
+          <t>https://www.seeedstudio.com/XIAO-ESP32S3-p-5627.html</t>
         </is>
       </c>
       <c r="I2" s="3" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/dp/B0H6XJGN3Z</t>
+          <t>https://www.amazon.com/dp/B0BYSB66S5</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>Plus boards ship WITHOUT pin headers: see the header and socket lines below. Mounted on the back, on sockets. The plain XIAO ESP32-S3 (https://www.amazon.com/dp/B0BYSB66S5) is interchangeable and runs the same 8 MB binary. AliExpress: https://www.aliexpress.us/item/3256808599305867.html</t>
+          <t>Primary. Seeed sells it with pin headers Un-Soldered or Pre-Soldered; Pre-Soldered makes the male header line below unnecessary. ALTERNATE if more memory is wanted: XIAO ESP32-S3 Plus (16 MB flash, SKU 102010671) https://www.seeedstudio.com/Seeed-Studio-XIAO-ESP32S3-Plus-p-6361.html / https://www.amazon.com/dp/B0H6XJGN3Z / https://www.aliexpress.us/item/3256808599305867.html - ships WITHOUT headers. Same footprint and the same 8 MB firmware binary on both. Mounted on the back, on sockets.</t>
         </is>
       </c>
     </row>
@@ -792,7 +792,7 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>Soldered to the XIAO, plugs into the XIAO sockets.</t>
+          <t>Soldered to the XIAO, plugs into the XIAO sockets. Skip if the XIAO was bought Pre-Soldered.</t>
         </is>
       </c>
     </row>

--- a/hardware/hot-info-orbs-xiao/bom/hot_info_orbs_xiao_bom.xlsx
+++ b/hardware/hot-info-orbs-xiao/bom/hot_info_orbs_xiao_bom.xlsx
@@ -10,7 +10,7 @@
     <sheet name="BOM" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'BOM'!$A$1:$J$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'BOM'!$A$1:$M$13</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -18,7 +18,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
+  </numFmts>
   <fonts count="3">
     <font>
       <name val="Calibri"/>
@@ -65,7 +67,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -74,12 +76,20 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -445,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J13"/>
+  <dimension ref="A1:M16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -457,7 +467,10 @@
     <col width="30" customWidth="1" min="7" max="7"/>
     <col width="40" customWidth="1" min="8" max="8"/>
     <col width="40" customWidth="1" min="9" max="9"/>
-    <col width="60" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="9" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="60" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -508,6 +521,21 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
+          <t>Price (Link 1)</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Pack qty</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Build cost</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
           <t>Notes</t>
         </is>
       </c>
@@ -554,7 +582,17 @@
           <t>https://www.amazon.com/dp/B0BYSB66S5</t>
         </is>
       </c>
-      <c r="J2" s="2" t="inlineStr">
+      <c r="J2" s="4" t="n">
+        <v>7.49</v>
+      </c>
+      <c r="K2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L2" s="4">
+        <f>ROUNDUP(C2/K2,0)*J2</f>
+        <v/>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
         <is>
           <t>Primary. Seeed sells it with pin headers Un-Soldered or Pre-Soldered; Pre-Soldered makes the male header line below unnecessary. ALTERNATE if more memory is wanted: XIAO ESP32-S3 Plus (16 MB flash, SKU 102010671) https://www.seeedstudio.com/Seeed-Studio-XIAO-ESP32S3-Plus-p-6361.html / https://www.amazon.com/dp/B0H6XJGN3Z / https://www.aliexpress.us/item/3256808599305867.html - ships WITHOUT headers. Same footprint and the same 8 MB firmware binary on both. Mounted on the back, on sockets.</t>
         </is>
@@ -602,7 +640,17 @@
           <t>https://www.aliexpress.us/item/3256813175276825.html</t>
         </is>
       </c>
-      <c r="J3" s="2" t="inlineStr">
+      <c r="J3" s="4" t="n">
+        <v>17.99</v>
+      </c>
+      <c r="K3" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="L3" s="4">
+        <f>ROUNDUP(C3/K3,0)*J3</f>
+        <v/>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
         <is>
           <t>Check the listing's pin order before buying; the footprint is pad 1 = VCC (+5V) .. pad 7 = RST. The module's own male header plugs into the female socket below. Lit area ~32.5 mm dia (docs/DISPLAY-EDGE-TEST.md).</t>
         </is>
@@ -646,7 +694,17 @@
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr"/>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="J4" s="4" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="K4" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L4" s="4">
+        <f>ROUNDUP(C4/K4,0)*J4</f>
+        <v/>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
         <is>
           <t>Choose the Diameter 35.5mm option on the listing (Scott, 2026-10-17); clears the ~32.5 mm lit area. No Amazon source found yet.</t>
         </is>
@@ -694,7 +752,17 @@
           <t>https://www.aliexpress.us/item/3256812879331298.html</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
+      <c r="J5" s="4" t="n">
+        <v>6.99</v>
+      </c>
+      <c r="K5" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="L5" s="4">
+        <f>ROUNDUP(C5/K5,0)*J5</f>
+        <v/>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>Not a schematic part: modeled inside the display footprint. 8.5 mm is the lift the 3D assumes; the marketplace sockets' body height is NOT verified. On AliExpress choose the 7P option.</t>
         </is>
@@ -742,9 +810,18 @@
           <t>https://www.aliexpress.us/item/3256812879331298.html</t>
         </is>
       </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>Same part as the display sockets; 7 per board in all.</t>
+      <c r="J6" s="4" t="n">
+        <v>6.99</v>
+      </c>
+      <c r="K6" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="L6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>Same part as the display sockets; 7 per board in all. Build cost 0: they come out of the line above's 60-pack.</t>
         </is>
       </c>
     </row>
@@ -790,105 +867,135 @@
           <t>https://www.aliexpress.us/item/3256806779943089.html</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="J7" s="4" t="n">
+        <v>6.29</v>
+      </c>
+      <c r="K7" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="L7" s="4">
+        <f>ROUNDUP(C7/K7,0)*J7</f>
+        <v/>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
         <is>
           <t>Soldered to the XIAO, plugs into the XIAO sockets. Skip if the XIAO was bought Pre-Soldered.</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="n">
+      <c r="A8" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="B8" s="4" t="inlineStr">
+      <c r="B8" s="5" t="inlineStr">
         <is>
           <t>SW1-SW3</t>
         </is>
       </c>
-      <c r="C8" s="4" t="n">
+      <c r="C8" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="D8" s="4" t="inlineStr">
+      <c r="D8" s="5" t="inlineStr">
         <is>
           <t>Tactile switch, right angle, 6x6 mm</t>
         </is>
       </c>
-      <c r="E8" s="4" t="inlineStr">
+      <c r="E8" s="5" t="inlineStr">
         <is>
           <t>SPST-NO, through hole, side actuated</t>
         </is>
       </c>
-      <c r="F8" s="4" t="inlineStr">
+      <c r="F8" s="5" t="inlineStr">
         <is>
           <t>SW_Tactile_SPST_Angled_PTS645Vx39-2LFS</t>
         </is>
       </c>
-      <c r="G8" s="4" t="inlineStr">
+      <c r="G8" s="5" t="inlineStr">
         <is>
           <t>C&amp;K PTS645VL39-2 LFS (footprint part)</t>
         </is>
       </c>
-      <c r="H8" s="5" t="inlineStr">
+      <c r="H8" s="6" t="inlineStr">
         <is>
           <t>https://www.amazon.com/dp/B008DS13P2</t>
         </is>
       </c>
-      <c r="I8" s="5" t="inlineStr">
+      <c r="I8" s="6" t="inlineStr">
         <is>
           <t>https://www.aliexpress.us/item/3256810140983087.html</t>
         </is>
       </c>
-      <c r="J8" s="4" t="inlineStr">
+      <c r="J8" s="7" t="n">
+        <v>7.39</v>
+      </c>
+      <c r="K8" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="L8" s="7">
+        <f>ROUNDUP(C8/K8,0)*J8</f>
+        <v/>
+      </c>
+      <c r="M8" s="5" t="inlineStr">
         <is>
           <t>FIT NOT VERIFIED: the footprint is the C&amp;K part (7.0 mm mounting-pin pitch); the uxcell 6x6x8 on Amazon lists 6.5 mm. Check one against the board before buying a lot. Exact part: https://lcsc.com/product-detail/Tactile-Switches_C-K-PTS645VL392LFS_C285523.html</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="n">
+      <c r="A9" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="B9" s="4" t="inlineStr">
+      <c r="B9" s="5" t="inlineStr">
         <is>
           <t>C1</t>
         </is>
       </c>
-      <c r="C9" s="4" t="n">
+      <c r="C9" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="D9" s="4" t="inlineStr">
-        <is>
-          <t>Electrolytic capacitor, +5V bulk</t>
-        </is>
-      </c>
-      <c r="E9" s="4" t="inlineStr">
-        <is>
-          <t>VALUE NOT IN SCHEMATIC - suggested 100 uF 16 V, 6.3 mm dia, 2.5 mm pitch</t>
-        </is>
-      </c>
-      <c r="F9" s="4" t="inlineStr">
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>Electrolytic capacitor 100 uF 16 V, +5V bulk</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>100 uF 16 V, 6.3 mm dia, 2.5 mm pitch</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="inlineStr">
         <is>
           <t>CP_Radial_D6.3mm_P2.50mm</t>
         </is>
       </c>
-      <c r="G9" s="4" t="inlineStr">
-        <is>
-          <t>Panasonic EEU-FC1C101H (suggested)</t>
-        </is>
-      </c>
-      <c r="H9" s="5" t="inlineStr">
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>Panasonic EEU-FC1C101H (reference)</t>
+        </is>
+      </c>
+      <c r="H9" s="6" t="inlineStr">
         <is>
           <t>https://www.amazon.com/dp/B0CPDF3HHB</t>
         </is>
       </c>
-      <c r="I9" s="5" t="inlineStr">
+      <c r="I9" s="6" t="inlineStr">
         <is>
           <t>https://www.aliexpress.us/item/3256812824344961.html</t>
         </is>
       </c>
-      <c r="J9" s="4" t="inlineStr">
-        <is>
-          <t>Schematic Value field holds the symbol name only - pick and record a value. The Amazon kit lists no dimensions: check 6.3 mm dia / 2.5 mm pitch. AliExpress is Nichicon 6.3x7. Height is on the back side; check enclosure clearance.</t>
+      <c r="J9" s="7" t="n">
+        <v>5.49</v>
+      </c>
+      <c r="K9" s="5" t="n">
+        <v>50</v>
+      </c>
+      <c r="L9" s="7">
+        <f>ROUNDUP(C9/K9,0)*J9</f>
+        <v/>
+      </c>
+      <c r="M9" s="5" t="inlineStr">
+        <is>
+          <t>Value set by Scott 2026-10-17 and now in the schematic. The Amazon listing gives no size, so 6.3 mm dia / 2.5 mm pitch is NOT VERIFIED for it; AliExpress is Nichicon 6.3x7. Height is on the back side; check enclosure clearance.</t>
         </is>
       </c>
     </row>
@@ -934,7 +1041,17 @@
           <t>https://www.aliexpress.us/item/3256811560978404.html</t>
         </is>
       </c>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="J10" s="4" t="n">
+        <v>6.99</v>
+      </c>
+      <c r="K10" s="2" t="n">
+        <v>120</v>
+      </c>
+      <c r="L10" s="4">
+        <f>ROUNDUP(C10/K10,0)*J10</f>
+        <v/>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
         <is>
           <t>Display RST hold-off with R1. Both listings are 5.08 mm pitch.</t>
         </is>
@@ -982,7 +1099,17 @@
           <t>https://www.aliexpress.us/item/3256807898146236.html</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
+      <c r="J11" s="4" t="n">
+        <v>4.99</v>
+      </c>
+      <c r="K11" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="L11" s="4">
+        <f>ROUNDUP(C11/K11,0)*J11</f>
+        <v/>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>Display RST pull-up to 3V3.</t>
         </is>
@@ -1030,7 +1157,17 @@
           <t>https://www.aliexpress.us/item/3256805704775238.html</t>
         </is>
       </c>
-      <c r="J12" s="2" t="inlineStr">
+      <c r="J12" s="4" t="n">
+        <v>7.49</v>
+      </c>
+      <c r="K12" s="2" t="n">
+        <v>120</v>
+      </c>
+      <c r="L12" s="4">
+        <f>ROUNDUP(C12/K12,0)*J12</f>
+        <v/>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>Standoffs/length set by the enclosure, not chosen yet.</t>
         </is>
@@ -1078,14 +1215,49 @@
           <t>https://www.pcbway.com/</t>
         </is>
       </c>
-      <c r="J13" s="2" t="inlineStr">
+      <c r="J13" s="4" t="inlineStr"/>
+      <c r="K13" s="2" t="inlineStr"/>
+      <c r="L13" s="4" t="inlineStr"/>
+      <c r="M13" s="2" t="inlineStr">
         <is>
           <t>Order the colors explicitly: the stackup colors only drive the 3D/STEP, not the gerbers.</t>
         </is>
       </c>
     </row>
+    <row r="15">
+      <c r="K15" s="8" t="inlineStr">
+        <is>
+          <t>Total, one build</t>
+        </is>
+      </c>
+      <c r="L15" s="9">
+        <f>SUM(L2:L13)</f>
+        <v/>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>Link 1 prices seen 2026-10-17, before shipping and tax. PCB not included: get a JLCPCB quote.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="K16" s="8" t="inlineStr">
+        <is>
+          <t>Per-board share</t>
+        </is>
+      </c>
+      <c r="L16" s="9">
+        <f>C2/K2*J2+C3/K3*J3+C4/K4*J4+C5/K5*J5+C6/K6*J6+C7/K7*J7+C8/K8*J8+C9/K9*J9+C10/K10*J10+C11/K11*J11+C12/K12*J12</f>
+        <v/>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>Each pack pro-rated over the boards it covers.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J13"/>
+  <autoFilter ref="A1:M13"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I2" r:id="rId2"/>

--- a/hardware/hot-info-orbs-xiao/bom/hot_info_orbs_xiao_bom.xlsx
+++ b/hardware/hot-info-orbs-xiao/bom/hot_info_orbs_xiao_bom.xlsx
@@ -21,7 +21,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
   </numFmts>
-  <fonts count="3">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -31,13 +31,21 @@
     </font>
     <font>
       <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
     <font>
       <color rgb="000563C1"/>
       <u val="single"/>
     </font>
+    <font>
+      <b val="1"/>
+      <sz val="12"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -46,7 +54,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D9D9D9"/>
+        <fgColor rgb="001F3A5F"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F2F5F9"/>
       </patternFill>
     </fill>
     <fill>
@@ -54,8 +67,13 @@
         <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00DCE6F1"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -63,33 +81,83 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00D0D7DE"/>
+      </left>
+      <right style="thin">
+        <color rgb="00D0D7DE"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D0D7DE"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D0D7DE"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -452,6 +520,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="001F3A5F"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -465,15 +534,15 @@
     <col width="42" customWidth="1" min="5" max="5"/>
     <col width="34" customWidth="1" min="6" max="6"/>
     <col width="30" customWidth="1" min="7" max="7"/>
-    <col width="40" customWidth="1" min="8" max="8"/>
-    <col width="40" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
     <col width="9" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
     <col width="60" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Item</t>
@@ -544,7 +613,7 @@
       <c r="A2" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" s="3" t="inlineStr">
         <is>
           <t>U2</t>
         </is>
@@ -552,105 +621,105 @@
       <c r="C2" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D2" s="4" t="inlineStr">
         <is>
           <t>Seeed Studio XIAO ESP32-S3</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="E2" s="4" t="inlineStr">
         <is>
           <t>ESP32-S3R8, 8 MB flash, 8 MB PSRAM; SKU 113991114</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="F2" s="4" t="inlineStr">
         <is>
           <t>XIAO-ESP32-S3-SOCKET</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="G2" s="4" t="inlineStr">
         <is>
           <t>113991114</t>
         </is>
       </c>
-      <c r="H2" s="3" t="inlineStr">
-        <is>
-          <t>https://www.seeedstudio.com/XIAO-ESP32S3-p-5627.html</t>
-        </is>
-      </c>
-      <c r="I2" s="3" t="inlineStr">
-        <is>
-          <t>https://www.amazon.com/dp/B0BYSB66S5</t>
-        </is>
-      </c>
-      <c r="J2" s="4" t="n">
+      <c r="H2" s="5" t="inlineStr">
+        <is>
+          <t>Seeed</t>
+        </is>
+      </c>
+      <c r="I2" s="5" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="J2" s="6" t="n">
         <v>7.49</v>
       </c>
       <c r="K2" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="L2" s="4">
+      <c r="L2" s="6">
         <f>ROUNDUP(C2/K2,0)*J2</f>
         <v/>
       </c>
-      <c r="M2" s="2" t="inlineStr">
+      <c r="M2" s="4" t="inlineStr">
         <is>
           <t>Primary. Seeed sells it with pin headers Un-Soldered or Pre-Soldered; Pre-Soldered makes the male header line below unnecessary. ALTERNATE if more memory is wanted: XIAO ESP32-S3 Plus (16 MB flash, SKU 102010671) https://www.seeedstudio.com/Seeed-Studio-XIAO-ESP32S3-Plus-p-6361.html / https://www.amazon.com/dp/B0H6XJGN3Z / https://www.aliexpress.us/item/3256808599305867.html - ships WITHOUT headers. Same footprint and the same 8 MB firmware binary on both. Mounted on the back, on sockets.</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="n">
+      <c r="A3" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B3" s="8" t="inlineStr">
         <is>
           <t>DS1-DS5</t>
         </is>
       </c>
-      <c r="C3" s="2" t="n">
+      <c r="C3" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="D3" s="9" t="inlineStr">
         <is>
           <t>1.28in round TFT, GC9A01, 240x240, 7-pin SPI</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="E3" s="9" t="inlineStr">
         <is>
           <t>7-pin 2.54 mm header, order VCC GND SCL SDA DC CS RST</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="F3" s="9" t="inlineStr">
         <is>
           <t>_Displays:GC9A01_SOCKET</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="G3" s="9" t="inlineStr">
         <is>
           <t>generic</t>
         </is>
       </c>
-      <c r="H3" s="3" t="inlineStr">
-        <is>
-          <t>https://www.amazon.com/dp/B0DJ13VW73</t>
-        </is>
-      </c>
-      <c r="I3" s="3" t="inlineStr">
-        <is>
-          <t>https://www.aliexpress.us/item/3256813175276825.html</t>
-        </is>
-      </c>
-      <c r="J3" s="4" t="n">
+      <c r="H3" s="10" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="I3" s="10" t="inlineStr">
+        <is>
+          <t>AliExpress</t>
+        </is>
+      </c>
+      <c r="J3" s="11" t="n">
         <v>17.99</v>
       </c>
-      <c r="K3" s="2" t="n">
+      <c r="K3" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="L3" s="4">
+      <c r="L3" s="11">
         <f>ROUNDUP(C3/K3,0)*J3</f>
         <v/>
       </c>
-      <c r="M3" s="2" t="inlineStr">
+      <c r="M3" s="9" t="inlineStr">
         <is>
           <t>Check the listing's pin order before buying; the footprint is pad 1 = VCC (+5V) .. pad 7 = RST. The module's own male header plugs into the female socket below. Lit area ~32.5 mm dia (docs/DISPLAY-EDGE-TEST.md).</t>
         </is>
@@ -660,7 +729,7 @@
       <c r="A4" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B4" s="3" t="inlineStr">
         <is>
           <t>LENS1-LENS5</t>
         </is>
@@ -668,101 +737,101 @@
       <c r="C4" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="D4" s="4" t="inlineStr">
         <is>
           <t>Display lens: mineral watch crystal, double dome</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="E4" s="4" t="inlineStr">
         <is>
           <t>35.5 mm dia, 2.0 mm thick</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="F4" s="4" t="inlineStr">
         <is>
           <t>enclosure part, no footprint</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="G4" s="4" t="inlineStr">
         <is>
           <t>generic</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr">
-        <is>
-          <t>https://www.aliexpress.us/item/3256806569387664.html</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr"/>
-      <c r="J4" s="4" t="n">
+      <c r="H4" s="5" t="inlineStr">
+        <is>
+          <t>AliExpress</t>
+        </is>
+      </c>
+      <c r="I4" s="4" t="inlineStr"/>
+      <c r="J4" s="6" t="n">
         <v>3.08</v>
       </c>
       <c r="K4" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="L4" s="4">
+      <c r="L4" s="6">
         <f>ROUNDUP(C4/K4,0)*J4</f>
         <v/>
       </c>
-      <c r="M4" s="2" t="inlineStr">
+      <c r="M4" s="4" t="inlineStr">
         <is>
           <t>Choose the Diameter 35.5mm option on the listing (Scott, 2026-10-17); clears the ~32.5 mm lit area. No Amazon source found yet.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="n">
+      <c r="A5" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B5" s="8" t="inlineStr">
         <is>
           <t>J (displays)</t>
         </is>
       </c>
-      <c r="C5" s="2" t="n">
+      <c r="C5" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="D5" s="9" t="inlineStr">
         <is>
           <t>Female socket 1x07, 2.54 mm, straight</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="E5" s="9" t="inlineStr">
         <is>
           <t>8.5 mm body, through hole</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F5" s="9" t="inlineStr">
         <is>
           <t>PinSocket_1x07_P2.54mm_Vertical (in GC9A01_SOCKET)</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="G5" s="9" t="inlineStr">
         <is>
           <t>Sullins PPTC071LFBN-RC (reference)</t>
         </is>
       </c>
-      <c r="H5" s="3" t="inlineStr">
-        <is>
-          <t>https://www.amazon.com/dp/B0GM7T6XWP</t>
-        </is>
-      </c>
-      <c r="I5" s="3" t="inlineStr">
-        <is>
-          <t>https://www.aliexpress.us/item/3256812879331298.html</t>
-        </is>
-      </c>
-      <c r="J5" s="4" t="n">
+      <c r="H5" s="10" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="I5" s="10" t="inlineStr">
+        <is>
+          <t>AliExpress</t>
+        </is>
+      </c>
+      <c r="J5" s="11" t="n">
         <v>6.99</v>
       </c>
-      <c r="K5" s="2" t="n">
+      <c r="K5" s="7" t="n">
         <v>60</v>
       </c>
-      <c r="L5" s="4">
+      <c r="L5" s="11">
         <f>ROUNDUP(C5/K5,0)*J5</f>
         <v/>
       </c>
-      <c r="M5" s="2" t="inlineStr">
+      <c r="M5" s="9" t="inlineStr">
         <is>
           <t>Not a schematic part: modeled inside the display footprint. 8.5 mm is the lift the 3D assumes; the marketplace sockets' body height is NOT verified. On AliExpress choose the 7P option.</t>
         </is>
@@ -772,7 +841,7 @@
       <c r="A6" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B6" s="3" t="inlineStr">
         <is>
           <t>J (XIAO)</t>
         </is>
@@ -780,222 +849,222 @@
       <c r="C6" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="D6" s="4" t="inlineStr">
         <is>
           <t>Female socket 1x07, 2.54 mm, straight</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="E6" s="4" t="inlineStr">
         <is>
           <t>8.5 mm body, through hole</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="F6" s="4" t="inlineStr">
         <is>
           <t>in XIAO-ESP32-S3-SOCKET</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="G6" s="4" t="inlineStr">
         <is>
           <t>Sullins PPTC071LFBN-RC (reference)</t>
         </is>
       </c>
-      <c r="H6" s="3" t="inlineStr">
-        <is>
-          <t>https://www.amazon.com/dp/B0GM7T6XWP</t>
-        </is>
-      </c>
-      <c r="I6" s="3" t="inlineStr">
-        <is>
-          <t>https://www.aliexpress.us/item/3256812879331298.html</t>
-        </is>
-      </c>
-      <c r="J6" s="4" t="n">
+      <c r="H6" s="5" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="I6" s="5" t="inlineStr">
+        <is>
+          <t>AliExpress</t>
+        </is>
+      </c>
+      <c r="J6" s="6" t="n">
         <v>6.99</v>
       </c>
       <c r="K6" s="2" t="n">
         <v>60</v>
       </c>
-      <c r="L6" s="4" t="n">
+      <c r="L6" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="M6" s="2" t="inlineStr">
+      <c r="M6" s="4" t="inlineStr">
         <is>
           <t>Same part as the display sockets; 7 per board in all. Build cost 0: they come out of the line above's 60-pack.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="n">
+      <c r="A7" s="7" t="n">
         <v>6</v>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B7" s="8" t="inlineStr">
         <is>
           <t>P (XIAO)</t>
         </is>
       </c>
-      <c r="C7" s="2" t="n">
+      <c r="C7" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="D7" s="9" t="inlineStr">
         <is>
           <t>Male header 1x07, 2.54 mm</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="E7" s="9" t="inlineStr">
         <is>
           <t>cut from a 1x40 breakaway strip (1 strip = 5 sets)</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="F7" s="9" t="inlineStr">
         <is>
           <t>in XIAO-ESP32-S3-SOCKET</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="G7" s="9" t="inlineStr">
         <is>
           <t>Sullins PRPC040SAAN-RC (reference)</t>
         </is>
       </c>
-      <c r="H7" s="3" t="inlineStr">
-        <is>
-          <t>https://www.amazon.com/dp/B0FRZW75VS</t>
-        </is>
-      </c>
-      <c r="I7" s="3" t="inlineStr">
-        <is>
-          <t>https://www.aliexpress.us/item/3256806779943089.html</t>
-        </is>
-      </c>
-      <c r="J7" s="4" t="n">
+      <c r="H7" s="10" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="I7" s="10" t="inlineStr">
+        <is>
+          <t>AliExpress</t>
+        </is>
+      </c>
+      <c r="J7" s="11" t="n">
         <v>6.29</v>
       </c>
-      <c r="K7" s="2" t="n">
+      <c r="K7" s="7" t="n">
         <v>100</v>
       </c>
-      <c r="L7" s="4">
+      <c r="L7" s="11">
         <f>ROUNDUP(C7/K7,0)*J7</f>
         <v/>
       </c>
-      <c r="M7" s="2" t="inlineStr">
+      <c r="M7" s="9" t="inlineStr">
         <is>
           <t>Soldered to the XIAO, plugs into the XIAO sockets. Skip if the XIAO was bought Pre-Soldered.</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="n">
+      <c r="A8" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="B8" s="5" t="inlineStr">
+      <c r="B8" s="13" t="inlineStr">
         <is>
           <t>SW1-SW3</t>
         </is>
       </c>
-      <c r="C8" s="5" t="n">
+      <c r="C8" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="D8" s="5" t="inlineStr">
+      <c r="D8" s="14" t="inlineStr">
         <is>
           <t>Tactile switch, right angle, 6x6 mm</t>
         </is>
       </c>
-      <c r="E8" s="5" t="inlineStr">
+      <c r="E8" s="14" t="inlineStr">
         <is>
           <t>SPST-NO, through hole, side actuated</t>
         </is>
       </c>
-      <c r="F8" s="5" t="inlineStr">
+      <c r="F8" s="14" t="inlineStr">
         <is>
           <t>SW_Tactile_SPST_Angled_PTS645Vx39-2LFS</t>
         </is>
       </c>
-      <c r="G8" s="5" t="inlineStr">
+      <c r="G8" s="14" t="inlineStr">
         <is>
           <t>C&amp;K PTS645VL39-2 LFS (footprint part)</t>
         </is>
       </c>
-      <c r="H8" s="6" t="inlineStr">
-        <is>
-          <t>https://www.amazon.com/dp/B008DS13P2</t>
-        </is>
-      </c>
-      <c r="I8" s="6" t="inlineStr">
-        <is>
-          <t>https://www.aliexpress.us/item/3256810140983087.html</t>
-        </is>
-      </c>
-      <c r="J8" s="7" t="n">
+      <c r="H8" s="15" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="I8" s="15" t="inlineStr">
+        <is>
+          <t>AliExpress</t>
+        </is>
+      </c>
+      <c r="J8" s="16" t="n">
         <v>7.39</v>
       </c>
-      <c r="K8" s="5" t="n">
+      <c r="K8" s="12" t="n">
         <v>20</v>
       </c>
-      <c r="L8" s="7">
+      <c r="L8" s="16">
         <f>ROUNDUP(C8/K8,0)*J8</f>
         <v/>
       </c>
-      <c r="M8" s="5" t="inlineStr">
+      <c r="M8" s="14" t="inlineStr">
         <is>
           <t>FIT NOT VERIFIED: the footprint is the C&amp;K part (7.0 mm mounting-pin pitch); the uxcell 6x6x8 on Amazon lists 6.5 mm. Check one against the board before buying a lot. Exact part: https://lcsc.com/product-detail/Tactile-Switches_C-K-PTS645VL392LFS_C285523.html</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="n">
+      <c r="A9" s="7" t="n">
         <v>8</v>
       </c>
-      <c r="B9" s="5" t="inlineStr">
+      <c r="B9" s="8" t="inlineStr">
         <is>
           <t>C1</t>
         </is>
       </c>
-      <c r="C9" s="5" t="n">
+      <c r="C9" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="D9" s="5" t="inlineStr">
+      <c r="D9" s="9" t="inlineStr">
         <is>
           <t>Electrolytic capacitor 100 uF 16 V, +5V bulk</t>
         </is>
       </c>
-      <c r="E9" s="5" t="inlineStr">
+      <c r="E9" s="9" t="inlineStr">
         <is>
           <t>100 uF 16 V, 6.3 mm dia, 2.5 mm pitch</t>
         </is>
       </c>
-      <c r="F9" s="5" t="inlineStr">
+      <c r="F9" s="9" t="inlineStr">
         <is>
           <t>CP_Radial_D6.3mm_P2.50mm</t>
         </is>
       </c>
-      <c r="G9" s="5" t="inlineStr">
+      <c r="G9" s="9" t="inlineStr">
         <is>
           <t>Panasonic EEU-FC1C101H (reference)</t>
         </is>
       </c>
-      <c r="H9" s="6" t="inlineStr">
-        <is>
-          <t>https://www.amazon.com/dp/B0CPDF3HHB</t>
-        </is>
-      </c>
-      <c r="I9" s="6" t="inlineStr">
-        <is>
-          <t>https://www.aliexpress.us/item/3256812824344961.html</t>
-        </is>
-      </c>
-      <c r="J9" s="7" t="n">
-        <v>5.49</v>
-      </c>
-      <c r="K9" s="5" t="n">
-        <v>50</v>
-      </c>
-      <c r="L9" s="7">
+      <c r="H9" s="10" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="I9" s="10" t="inlineStr">
+        <is>
+          <t>AliExpress</t>
+        </is>
+      </c>
+      <c r="J9" s="11" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="K9" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="L9" s="11">
         <f>ROUNDUP(C9/K9,0)*J9</f>
         <v/>
       </c>
-      <c r="M9" s="5" t="inlineStr">
-        <is>
-          <t>Value set by Scott 2026-10-17 and now in the schematic. The Amazon listing gives no size, so 6.3 mm dia / 2.5 mm pitch is NOT VERIFIED for it; AliExpress is Nichicon 6.3x7. Height is on the back side; check enclosure clearance.</t>
+      <c r="M9" s="9" t="inlineStr">
+        <is>
+          <t>Value set by Scott 2026-10-17. Both listings state 6.3 mm dia (Amazon 6.3x11, AliExpress Nichicon 6.3x7); neither states pitch, and 6.3 mm radials are 2.5 mm by convention. Mounted on the back: the 11 mm Amazon part stands 4 mm taller than the AliExpress one, so check enclosure clearance.</t>
         </is>
       </c>
     </row>
@@ -1003,7 +1072,7 @@
       <c r="A10" s="2" t="n">
         <v>9</v>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B10" s="3" t="inlineStr">
         <is>
           <t>C2</t>
         </is>
@@ -1011,105 +1080,105 @@
       <c r="C10" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="D10" s="4" t="inlineStr">
         <is>
           <t>Ceramic capacitor 1 uF (105)</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="E10" s="4" t="inlineStr">
         <is>
           <t>50 V, radial, 5.08 mm lead spacing</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="F10" s="4" t="inlineStr">
         <is>
           <t>C_Disc_D5.0mm_W2.5mm_P5.00mm</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="G10" s="4" t="inlineStr">
         <is>
           <t>KEMET C330C105K5R5TA7301 (reference)</t>
         </is>
       </c>
-      <c r="H10" s="3" t="inlineStr">
-        <is>
-          <t>https://www.amazon.com/dp/B08BF91KY3</t>
-        </is>
-      </c>
-      <c r="I10" s="3" t="inlineStr">
-        <is>
-          <t>https://www.aliexpress.us/item/3256811560978404.html</t>
-        </is>
-      </c>
-      <c r="J10" s="4" t="n">
+      <c r="H10" s="5" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="I10" s="5" t="inlineStr">
+        <is>
+          <t>AliExpress</t>
+        </is>
+      </c>
+      <c r="J10" s="6" t="n">
         <v>6.99</v>
       </c>
       <c r="K10" s="2" t="n">
         <v>120</v>
       </c>
-      <c r="L10" s="4">
+      <c r="L10" s="6">
         <f>ROUNDUP(C10/K10,0)*J10</f>
         <v/>
       </c>
-      <c r="M10" s="2" t="inlineStr">
+      <c r="M10" s="4" t="inlineStr">
         <is>
           <t>Display RST hold-off with R1. Both listings are 5.08 mm pitch.</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="n">
+      <c r="A11" s="7" t="n">
         <v>10</v>
       </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="B11" s="8" t="inlineStr">
         <is>
           <t>R1</t>
         </is>
       </c>
-      <c r="C11" s="2" t="n">
+      <c r="C11" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="D11" s="9" t="inlineStr">
         <is>
           <t>Resistor 10k</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="E11" s="9" t="inlineStr">
         <is>
           <t>1/4 W 5 % carbon film, axial, 10.16 mm pitch</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="F11" s="9" t="inlineStr">
         <is>
           <t>R_Axial_DIN0207_L6.3mm_D2.5mm_P10.16mm_Horizontal</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="G11" s="9" t="inlineStr">
         <is>
           <t>Stackpole CF14JT10K0 (reference)</t>
         </is>
       </c>
-      <c r="H11" s="3" t="inlineStr">
-        <is>
-          <t>https://www.amazon.com/dp/B0CL9KXXZB</t>
-        </is>
-      </c>
-      <c r="I11" s="3" t="inlineStr">
-        <is>
-          <t>https://www.aliexpress.us/item/3256807898146236.html</t>
-        </is>
-      </c>
-      <c r="J11" s="4" t="n">
+      <c r="H11" s="10" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="I11" s="10" t="inlineStr">
+        <is>
+          <t>AliExpress</t>
+        </is>
+      </c>
+      <c r="J11" s="11" t="n">
         <v>4.99</v>
       </c>
-      <c r="K11" s="2" t="n">
+      <c r="K11" s="7" t="n">
         <v>100</v>
       </c>
-      <c r="L11" s="4">
+      <c r="L11" s="11">
         <f>ROUNDUP(C11/K11,0)*J11</f>
         <v/>
       </c>
-      <c r="M11" s="2" t="inlineStr">
+      <c r="M11" s="9" t="inlineStr">
         <is>
           <t>Display RST pull-up to 3V3.</t>
         </is>
@@ -1119,7 +1188,7 @@
       <c r="A12" s="2" t="n">
         <v>11</v>
       </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="B12" s="3" t="inlineStr">
         <is>
           <t>H1-H7</t>
         </is>
@@ -1127,130 +1196,130 @@
       <c r="C12" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="D12" s="4" t="inlineStr">
         <is>
           <t>M3 screw (mounting)</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="E12" s="4" t="inlineStr">
         <is>
           <t>M3-0.5, socket head; 3.2 mm holes</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="F12" s="4" t="inlineStr">
         <is>
           <t>Edge.Cuts circles, no footprint</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="G12" s="4" t="inlineStr">
         <is>
           <t>M3 x 6 DIN 912 class 12.9 (length depends on the enclosure)</t>
         </is>
       </c>
-      <c r="H12" s="3" t="inlineStr">
-        <is>
-          <t>https://www.amazon.com/dp/B0DJQH3WSX</t>
-        </is>
-      </c>
-      <c r="I12" s="3" t="inlineStr">
-        <is>
-          <t>https://www.aliexpress.us/item/3256805704775238.html</t>
-        </is>
-      </c>
-      <c r="J12" s="4" t="n">
+      <c r="H12" s="5" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="I12" s="5" t="inlineStr">
+        <is>
+          <t>AliExpress</t>
+        </is>
+      </c>
+      <c r="J12" s="6" t="n">
         <v>7.49</v>
       </c>
       <c r="K12" s="2" t="n">
         <v>120</v>
       </c>
-      <c r="L12" s="4">
+      <c r="L12" s="6">
         <f>ROUNDUP(C12/K12,0)*J12</f>
         <v/>
       </c>
-      <c r="M12" s="2" t="inlineStr">
+      <c r="M12" s="4" t="inlineStr">
         <is>
           <t>Standoffs/length set by the enclosure, not chosen yet.</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="n">
+      <c r="A13" s="7" t="n">
         <v>12</v>
       </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="B13" s="8" t="inlineStr">
         <is>
           <t>PCB</t>
         </is>
       </c>
-      <c r="C13" s="2" t="n">
+      <c r="C13" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="D13" s="9" t="inlineStr">
         <is>
           <t>Bare board</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="E13" s="9" t="inlineStr">
         <is>
           <t>2 layer, 1.6 mm, 198.82 x 47.78 mm, WHITE solder mask, BLACK silkscreen</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="F13" s="9" t="inlineStr">
         <is>
           <t>hot_info_orbs_xiao.kicad_pcb</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="G13" s="9" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H13" s="3" t="inlineStr">
-        <is>
-          <t>https://jlcpcb.com/quote/pcbOrderFaq/PCB%20Color</t>
-        </is>
-      </c>
-      <c r="I13" s="3" t="inlineStr">
-        <is>
-          <t>https://www.pcbway.com/</t>
-        </is>
-      </c>
-      <c r="J13" s="4" t="inlineStr"/>
-      <c r="K13" s="2" t="inlineStr"/>
-      <c r="L13" s="4" t="inlineStr"/>
-      <c r="M13" s="2" t="inlineStr">
+      <c r="H13" s="10" t="inlineStr">
+        <is>
+          <t>JLCPCB</t>
+        </is>
+      </c>
+      <c r="I13" s="10" t="inlineStr">
+        <is>
+          <t>PCBWay</t>
+        </is>
+      </c>
+      <c r="J13" s="11" t="inlineStr"/>
+      <c r="K13" s="7" t="inlineStr"/>
+      <c r="L13" s="11" t="inlineStr"/>
+      <c r="M13" s="9" t="inlineStr">
         <is>
           <t>Order the colors explicitly: the stackup colors only drive the 3D/STEP, not the gerbers.</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="K15" s="8" t="inlineStr">
+      <c r="K15" s="17" t="inlineStr">
         <is>
           <t>Total, one build</t>
         </is>
       </c>
-      <c r="L15" s="9">
+      <c r="L15" s="18">
         <f>SUM(L2:L13)</f>
         <v/>
       </c>
-      <c r="M15" s="2" t="inlineStr">
+      <c r="M15" s="19" t="inlineStr">
         <is>
           <t>Link 1 prices seen 2026-10-17, before shipping and tax. PCB not included: get a JLCPCB quote.</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="K16" s="8" t="inlineStr">
+      <c r="K16" s="17" t="inlineStr">
         <is>
           <t>Per-board share</t>
         </is>
       </c>
-      <c r="L16" s="9">
+      <c r="L16" s="18">
         <f>C2/K2*J2+C3/K3*J3+C4/K4*J4+C5/K5*J5+C6/K6*J6+C7/K7*J7+C8/K8*J8+C9/K9*J9+C10/K10*J10+C11/K11*J11+C12/K12*J12</f>
         <v/>
       </c>
-      <c r="M16" s="2" t="inlineStr">
+      <c r="M16" s="19" t="inlineStr">
         <is>
           <t>Each pack pro-rated over the boards it covers.</t>
         </is>

--- a/hardware/hot-info-orbs-xiao/bom/hot_info_orbs_xiao_bom.xlsx
+++ b/hardware/hot-info-orbs-xiao/bom/hot_info_orbs_xiao_bom.xlsx
@@ -10,7 +10,7 @@
     <sheet name="BOM" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'BOM'!$A$1:$M$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'BOM'!$A$1:$M$14</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -21,7 +21,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -43,6 +43,12 @@
     <font>
       <b val="1"/>
       <sz val="12"/>
+    </font>
+    <font>
+      <i val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
     </font>
   </fonts>
   <fills count="6">
@@ -99,7 +105,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -117,7 +123,7 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
@@ -132,7 +138,7 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
@@ -147,7 +153,7 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -156,6 +162,12 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -524,7 +536,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M16"/>
+  <dimension ref="A1:M20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -731,7 +743,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>LENS1-LENS5</t>
+          <t>LENS1-LENS5 (glass)</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
@@ -775,7 +787,7 @@
       </c>
       <c r="M4" s="4" t="inlineStr">
         <is>
-          <t>Choose the Diameter 35.5mm option on the listing (Scott, 2026-10-17); clears the ~32.5 mm lit area. No Amazon source found yet.</t>
+          <t>OPTIONAL, not in the build total (priced as an add-on below it). Choose the Diameter 35.5mm option on the listing (Scott, 2026-10-17); clears the ~32.5 mm lit area. No Amazon source found yet.</t>
         </is>
       </c>
     </row>
@@ -785,7 +797,7 @@
       </c>
       <c r="B5" s="8" t="inlineStr">
         <is>
-          <t>J (displays)</t>
+          <t>LENS1-LENS5 (acrylic)</t>
         </is>
       </c>
       <c r="C5" s="7" t="n">
@@ -793,47 +805,46 @@
       </c>
       <c r="D5" s="9" t="inlineStr">
         <is>
-          <t>Female socket 1x07, 2.54 mm, straight</t>
+          <t>Display lens: laser-cut clear acrylic disc</t>
         </is>
       </c>
       <c r="E5" s="9" t="inlineStr">
         <is>
-          <t>8.5 mm body, through hole</t>
+          <t>35.5 mm dia, thickness TBD</t>
         </is>
       </c>
       <c r="F5" s="9" t="inlineStr">
         <is>
-          <t>PinSocket_1x07_P2.54mm_Vertical (in GC9A01_SOCKET)</t>
+          <t>enclosure part, no footprint</t>
         </is>
       </c>
       <c r="G5" s="9" t="inlineStr">
         <is>
-          <t>Sullins PPTC071LFBN-RC (reference)</t>
-        </is>
-      </c>
-      <c r="H5" s="10" t="inlineStr">
-        <is>
-          <t>Amazon</t>
-        </is>
-      </c>
-      <c r="I5" s="10" t="inlineStr">
-        <is>
-          <t>AliExpress</t>
-        </is>
-      </c>
-      <c r="J5" s="11" t="n">
-        <v>6.99</v>
+          <t>cut in-house</t>
+        </is>
+      </c>
+      <c r="H5" s="9" t="inlineStr">
+        <is>
+          <t>in-house (laser)</t>
+        </is>
+      </c>
+      <c r="I5" s="9" t="inlineStr"/>
+      <c r="J5" s="11" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
       </c>
       <c r="K5" s="7" t="n">
-        <v>60</v>
-      </c>
-      <c r="L5" s="11">
-        <f>ROUNDUP(C5/K5,0)*J5</f>
-        <v/>
+        <v>1</v>
+      </c>
+      <c r="L5" s="11" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
       </c>
       <c r="M5" s="9" t="inlineStr">
         <is>
-          <t>Not a schematic part: modeled inside the display footprint. 8.5 mm is the lift the 3D assumes; the marketplace sockets' body height is NOT verified. On AliExpress choose the 7P option.</t>
+          <t>OPTIONAL alternative to the glass lens, price TBD (Scott, 2026-10-17). Flat, so no dome. Same 35.5 mm diameter as the glass; the bezel has to allow for whichever thickness is chosen.</t>
         </is>
       </c>
     </row>
@@ -843,11 +854,11 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>J (XIAO)</t>
+          <t>J (displays)</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
@@ -861,7 +872,7 @@
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>in XIAO-ESP32-S3-SOCKET</t>
+          <t>PinSocket_1x07_P2.54mm_Vertical (in GC9A01_SOCKET)</t>
         </is>
       </c>
       <c r="G6" s="4" t="inlineStr">
@@ -885,12 +896,13 @@
       <c r="K6" s="2" t="n">
         <v>60</v>
       </c>
-      <c r="L6" s="6" t="n">
-        <v>0</v>
+      <c r="L6" s="6">
+        <f>ROUNDUP(C6/K6,0)*J6</f>
+        <v/>
       </c>
       <c r="M6" s="4" t="inlineStr">
         <is>
-          <t>Same part as the display sockets; 7 per board in all. Build cost 0: they come out of the line above's 60-pack.</t>
+          <t>Not a schematic part: modeled inside the display footprint. 8.5 mm is the lift the 3D assumes; the marketplace sockets' body height is NOT verified. On AliExpress choose the 7P option.</t>
         </is>
       </c>
     </row>
@@ -900,7 +912,7 @@
       </c>
       <c r="B7" s="8" t="inlineStr">
         <is>
-          <t>P (XIAO)</t>
+          <t>J (XIAO)</t>
         </is>
       </c>
       <c r="C7" s="7" t="n">
@@ -908,163 +920,162 @@
       </c>
       <c r="D7" s="9" t="inlineStr">
         <is>
+          <t>Female socket 1x07, 2.54 mm, straight</t>
+        </is>
+      </c>
+      <c r="E7" s="9" t="inlineStr">
+        <is>
+          <t>8.5 mm body, through hole</t>
+        </is>
+      </c>
+      <c r="F7" s="9" t="inlineStr">
+        <is>
+          <t>in XIAO-ESP32-S3-SOCKET</t>
+        </is>
+      </c>
+      <c r="G7" s="9" t="inlineStr">
+        <is>
+          <t>Sullins PPTC071LFBN-RC (reference)</t>
+        </is>
+      </c>
+      <c r="H7" s="10" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="I7" s="10" t="inlineStr">
+        <is>
+          <t>AliExpress</t>
+        </is>
+      </c>
+      <c r="J7" s="11" t="n">
+        <v>6.99</v>
+      </c>
+      <c r="K7" s="7" t="n">
+        <v>60</v>
+      </c>
+      <c r="L7" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" s="9" t="inlineStr">
+        <is>
+          <t>Same part as the display sockets; 7 per board in all. Build cost 0: they come out of the line above's 60-pack.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>P (XIAO)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
           <t>Male header 1x07, 2.54 mm</t>
         </is>
       </c>
-      <c r="E7" s="9" t="inlineStr">
+      <c r="E8" s="4" t="inlineStr">
         <is>
           <t>cut from a 1x40 breakaway strip (1 strip = 5 sets)</t>
         </is>
       </c>
-      <c r="F7" s="9" t="inlineStr">
+      <c r="F8" s="4" t="inlineStr">
         <is>
           <t>in XIAO-ESP32-S3-SOCKET</t>
         </is>
       </c>
-      <c r="G7" s="9" t="inlineStr">
+      <c r="G8" s="4" t="inlineStr">
         <is>
           <t>Sullins PRPC040SAAN-RC (reference)</t>
         </is>
       </c>
-      <c r="H7" s="10" t="inlineStr">
+      <c r="H8" s="5" t="inlineStr">
         <is>
           <t>Amazon</t>
         </is>
       </c>
-      <c r="I7" s="10" t="inlineStr">
+      <c r="I8" s="5" t="inlineStr">
         <is>
           <t>AliExpress</t>
         </is>
       </c>
-      <c r="J7" s="11" t="n">
+      <c r="J8" s="6" t="n">
         <v>6.29</v>
       </c>
-      <c r="K7" s="7" t="n">
+      <c r="K8" s="2" t="n">
         <v>100</v>
       </c>
-      <c r="L7" s="11">
-        <f>ROUNDUP(C7/K7,0)*J7</f>
-        <v/>
-      </c>
-      <c r="M7" s="9" t="inlineStr">
-        <is>
-          <t>Soldered to the XIAO, plugs into the XIAO sockets. Skip if the XIAO was bought Pre-Soldered.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="12" t="n">
-        <v>7</v>
-      </c>
-      <c r="B8" s="13" t="inlineStr">
-        <is>
-          <t>SW1-SW3</t>
-        </is>
-      </c>
-      <c r="C8" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="D8" s="14" t="inlineStr">
-        <is>
-          <t>Tactile switch, right angle, 6x6 mm</t>
-        </is>
-      </c>
-      <c r="E8" s="14" t="inlineStr">
-        <is>
-          <t>SPST-NO, through hole, side actuated</t>
-        </is>
-      </c>
-      <c r="F8" s="14" t="inlineStr">
-        <is>
-          <t>SW_Tactile_SPST_Angled_PTS645Vx39-2LFS</t>
-        </is>
-      </c>
-      <c r="G8" s="14" t="inlineStr">
-        <is>
-          <t>C&amp;K PTS645VL39-2 LFS (footprint part)</t>
-        </is>
-      </c>
-      <c r="H8" s="15" t="inlineStr">
-        <is>
-          <t>Amazon</t>
-        </is>
-      </c>
-      <c r="I8" s="15" t="inlineStr">
-        <is>
-          <t>AliExpress</t>
-        </is>
-      </c>
-      <c r="J8" s="16" t="n">
-        <v>7.39</v>
-      </c>
-      <c r="K8" s="12" t="n">
-        <v>20</v>
-      </c>
-      <c r="L8" s="16">
+      <c r="L8" s="6">
         <f>ROUNDUP(C8/K8,0)*J8</f>
         <v/>
       </c>
-      <c r="M8" s="14" t="inlineStr">
-        <is>
-          <t>FIT NOT VERIFIED: the footprint is the C&amp;K part (7.0 mm mounting-pin pitch); the uxcell 6x6x8 on Amazon lists 6.5 mm. Check one against the board before buying a lot. Exact part: https://lcsc.com/product-detail/Tactile-Switches_C-K-PTS645VL392LFS_C285523.html</t>
+      <c r="M8" s="4" t="inlineStr">
+        <is>
+          <t>Soldered to the XIAO, plugs into the XIAO sockets. Skip if the XIAO was bought Pre-Soldered.</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="7" t="n">
+      <c r="A9" s="12" t="n">
         <v>8</v>
       </c>
-      <c r="B9" s="8" t="inlineStr">
-        <is>
-          <t>C1</t>
-        </is>
-      </c>
-      <c r="C9" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="D9" s="9" t="inlineStr">
-        <is>
-          <t>Electrolytic capacitor 100 uF 16 V, +5V bulk</t>
-        </is>
-      </c>
-      <c r="E9" s="9" t="inlineStr">
-        <is>
-          <t>100 uF 16 V, 6.3 mm dia, 2.5 mm pitch</t>
-        </is>
-      </c>
-      <c r="F9" s="9" t="inlineStr">
-        <is>
-          <t>CP_Radial_D6.3mm_P2.50mm</t>
-        </is>
-      </c>
-      <c r="G9" s="9" t="inlineStr">
-        <is>
-          <t>Panasonic EEU-FC1C101H (reference)</t>
-        </is>
-      </c>
-      <c r="H9" s="10" t="inlineStr">
+      <c r="B9" s="13" t="inlineStr">
+        <is>
+          <t>SW1-SW3</t>
+        </is>
+      </c>
+      <c r="C9" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="D9" s="14" t="inlineStr">
+        <is>
+          <t>Tactile switch, right angle, 6x6 mm</t>
+        </is>
+      </c>
+      <c r="E9" s="14" t="inlineStr">
+        <is>
+          <t>SPST-NO, through hole, side actuated</t>
+        </is>
+      </c>
+      <c r="F9" s="14" t="inlineStr">
+        <is>
+          <t>SW_Tactile_SPST_Angled_PTS645Vx39-2LFS</t>
+        </is>
+      </c>
+      <c r="G9" s="14" t="inlineStr">
+        <is>
+          <t>C&amp;K PTS645VL39-2 LFS (footprint part)</t>
+        </is>
+      </c>
+      <c r="H9" s="15" t="inlineStr">
         <is>
           <t>Amazon</t>
         </is>
       </c>
-      <c r="I9" s="10" t="inlineStr">
+      <c r="I9" s="15" t="inlineStr">
         <is>
           <t>AliExpress</t>
         </is>
       </c>
-      <c r="J9" s="11" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="K9" s="7" t="n">
-        <v>10</v>
-      </c>
-      <c r="L9" s="11">
+      <c r="J9" s="16" t="n">
+        <v>7.39</v>
+      </c>
+      <c r="K9" s="12" t="n">
+        <v>20</v>
+      </c>
+      <c r="L9" s="16">
         <f>ROUNDUP(C9/K9,0)*J9</f>
         <v/>
       </c>
-      <c r="M9" s="9" t="inlineStr">
-        <is>
-          <t>Value set by Scott 2026-10-17. Both listings state 6.3 mm dia (Amazon 6.3x11, AliExpress Nichicon 6.3x7); neither states pitch, and 6.3 mm radials are 2.5 mm by convention. Mounted on the back: the 11 mm Amazon part stands 4 mm taller than the AliExpress one, so check enclosure clearance.</t>
+      <c r="M9" s="14" t="inlineStr">
+        <is>
+          <t>FIT NOT VERIFIED: the footprint is the C&amp;K part (7.0 mm mounting-pin pitch); the uxcell 6x6x8 on Amazon lists 6.5 mm. Check one against the board before buying a lot. Exact part: https://lcsc.com/product-detail/Tactile-Switches_C-K-PTS645VL392LFS_C285523.html</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1085,7 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>C2</t>
+          <t>C1</t>
         </is>
       </c>
       <c r="C10" s="2" t="n">
@@ -1082,22 +1093,22 @@
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>Ceramic capacitor 1 uF (105)</t>
+          <t>Electrolytic capacitor 100 uF 16 V, +5V bulk</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>50 V, radial, 5.08 mm lead spacing</t>
+          <t>100 uF 16 V, 6.3 mm dia, 2.5 mm pitch</t>
         </is>
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>C_Disc_D5.0mm_W2.5mm_P5.00mm</t>
+          <t>CP_Radial_D6.3mm_P2.50mm</t>
         </is>
       </c>
       <c r="G10" s="4" t="inlineStr">
         <is>
-          <t>KEMET C330C105K5R5TA7301 (reference)</t>
+          <t>Panasonic EEU-FC1C101H (reference)</t>
         </is>
       </c>
       <c r="H10" s="5" t="inlineStr">
@@ -1111,10 +1122,10 @@
         </is>
       </c>
       <c r="J10" s="6" t="n">
-        <v>6.99</v>
+        <v>6.6</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>120</v>
+        <v>10</v>
       </c>
       <c r="L10" s="6">
         <f>ROUNDUP(C10/K10,0)*J10</f>
@@ -1122,7 +1133,7 @@
       </c>
       <c r="M10" s="4" t="inlineStr">
         <is>
-          <t>Display RST hold-off with R1. Both listings are 5.08 mm pitch.</t>
+          <t>Value set by Scott 2026-10-17. Both listings state 6.3 mm dia (Amazon 6.3x11, AliExpress Nichicon 6.3x7); neither states pitch, and 6.3 mm radials are 2.5 mm by convention. Mounted on the back: the 11 mm Amazon part stands 4 mm taller than the AliExpress one, so check enclosure clearance.</t>
         </is>
       </c>
     </row>
@@ -1132,7 +1143,7 @@
       </c>
       <c r="B11" s="8" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>C2</t>
         </is>
       </c>
       <c r="C11" s="7" t="n">
@@ -1140,22 +1151,22 @@
       </c>
       <c r="D11" s="9" t="inlineStr">
         <is>
-          <t>Resistor 10k</t>
+          <t>Ceramic capacitor 1 uF (105)</t>
         </is>
       </c>
       <c r="E11" s="9" t="inlineStr">
         <is>
-          <t>1/4 W 5 % carbon film, axial, 10.16 mm pitch</t>
+          <t>50 V, radial, 5.08 mm lead spacing</t>
         </is>
       </c>
       <c r="F11" s="9" t="inlineStr">
         <is>
-          <t>R_Axial_DIN0207_L6.3mm_D2.5mm_P10.16mm_Horizontal</t>
+          <t>C_Disc_D5.0mm_W2.5mm_P5.00mm</t>
         </is>
       </c>
       <c r="G11" s="9" t="inlineStr">
         <is>
-          <t>Stackpole CF14JT10K0 (reference)</t>
+          <t>KEMET C330C105K5R5TA7301 (reference)</t>
         </is>
       </c>
       <c r="H11" s="10" t="inlineStr">
@@ -1169,10 +1180,10 @@
         </is>
       </c>
       <c r="J11" s="11" t="n">
-        <v>4.99</v>
+        <v>6.99</v>
       </c>
       <c r="K11" s="7" t="n">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="L11" s="11">
         <f>ROUNDUP(C11/K11,0)*J11</f>
@@ -1180,7 +1191,7 @@
       </c>
       <c r="M11" s="9" t="inlineStr">
         <is>
-          <t>Display RST pull-up to 3V3.</t>
+          <t>Display RST hold-off with R1. Both listings are 5.08 mm pitch.</t>
         </is>
       </c>
     </row>
@@ -1190,30 +1201,30 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>H1-H7</t>
+          <t>R1</t>
         </is>
       </c>
       <c r="C12" s="2" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>M3 screw (mounting)</t>
+          <t>Resistor 10k</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>M3-0.5, socket head; 3.2 mm holes</t>
+          <t>1/4 W 5 % carbon film, axial, 10.16 mm pitch</t>
         </is>
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>Edge.Cuts circles, no footprint</t>
+          <t>R_Axial_DIN0207_L6.3mm_D2.5mm_P10.16mm_Horizontal</t>
         </is>
       </c>
       <c r="G12" s="4" t="inlineStr">
         <is>
-          <t>M3 x 6 DIN 912 class 12.9 (length depends on the enclosure)</t>
+          <t>Stackpole CF14JT10K0 (reference)</t>
         </is>
       </c>
       <c r="H12" s="5" t="inlineStr">
@@ -1227,10 +1238,10 @@
         </is>
       </c>
       <c r="J12" s="6" t="n">
-        <v>7.49</v>
+        <v>4.99</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="L12" s="6">
         <f>ROUNDUP(C12/K12,0)*J12</f>
@@ -1238,7 +1249,7 @@
       </c>
       <c r="M12" s="4" t="inlineStr">
         <is>
-          <t>Standoffs/length set by the enclosure, not chosen yet.</t>
+          <t>Display RST pull-up to 3V3.</t>
         </is>
       </c>
     </row>
@@ -1248,109 +1259,216 @@
       </c>
       <c r="B13" s="8" t="inlineStr">
         <is>
+          <t>H1-H7</t>
+        </is>
+      </c>
+      <c r="C13" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="D13" s="9" t="inlineStr">
+        <is>
+          <t>M3 screw (mounting)</t>
+        </is>
+      </c>
+      <c r="E13" s="9" t="inlineStr">
+        <is>
+          <t>M3-0.5, socket head; 3.2 mm holes</t>
+        </is>
+      </c>
+      <c r="F13" s="9" t="inlineStr">
+        <is>
+          <t>Edge.Cuts circles, no footprint</t>
+        </is>
+      </c>
+      <c r="G13" s="9" t="inlineStr">
+        <is>
+          <t>M3 x 6 DIN 912 class 12.9 (length depends on the enclosure)</t>
+        </is>
+      </c>
+      <c r="H13" s="10" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="I13" s="10" t="inlineStr">
+        <is>
+          <t>AliExpress</t>
+        </is>
+      </c>
+      <c r="J13" s="11" t="n">
+        <v>7.49</v>
+      </c>
+      <c r="K13" s="7" t="n">
+        <v>120</v>
+      </c>
+      <c r="L13" s="11">
+        <f>ROUNDUP(C13/K13,0)*J13</f>
+        <v/>
+      </c>
+      <c r="M13" s="9" t="inlineStr">
+        <is>
+          <t>Standoffs/length set by the enclosure, not chosen yet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
           <t>PCB</t>
         </is>
       </c>
-      <c r="C13" s="7" t="n">
+      <c r="C14" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="D13" s="9" t="inlineStr">
+      <c r="D14" s="4" t="inlineStr">
         <is>
           <t>Bare board</t>
         </is>
       </c>
-      <c r="E13" s="9" t="inlineStr">
+      <c r="E14" s="4" t="inlineStr">
         <is>
           <t>2 layer, 1.6 mm, 198.82 x 47.78 mm, WHITE solder mask, BLACK silkscreen</t>
         </is>
       </c>
-      <c r="F13" s="9" t="inlineStr">
+      <c r="F14" s="4" t="inlineStr">
         <is>
           <t>hot_info_orbs_xiao.kicad_pcb</t>
         </is>
       </c>
-      <c r="G13" s="9" t="inlineStr">
+      <c r="G14" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H13" s="10" t="inlineStr">
+      <c r="H14" s="5" t="inlineStr">
         <is>
           <t>JLCPCB</t>
         </is>
       </c>
-      <c r="I13" s="10" t="inlineStr">
+      <c r="I14" s="5" t="inlineStr">
         <is>
           <t>PCBWay</t>
         </is>
       </c>
-      <c r="J13" s="11" t="inlineStr"/>
-      <c r="K13" s="7" t="inlineStr"/>
-      <c r="L13" s="11" t="inlineStr"/>
-      <c r="M13" s="9" t="inlineStr">
+      <c r="J14" s="6" t="inlineStr"/>
+      <c r="K14" s="2" t="inlineStr"/>
+      <c r="L14" s="6" t="inlineStr"/>
+      <c r="M14" s="4" t="inlineStr">
         <is>
           <t>Order the colors explicitly: the stackup colors only drive the 3D/STEP, not the gerbers.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="K15" s="17" t="inlineStr">
-        <is>
-          <t>Total, one build</t>
-        </is>
-      </c>
-      <c r="L15" s="18">
-        <f>SUM(L2:L13)</f>
-        <v/>
-      </c>
-      <c r="M15" s="19" t="inlineStr">
-        <is>
-          <t>Link 1 prices seen 2026-10-17, before shipping and tax. PCB not included: get a JLCPCB quote.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="K16" s="17" t="inlineStr">
         <is>
+          <t>Total, one build</t>
+        </is>
+      </c>
+      <c r="L16" s="18">
+        <f>L2+L3+L6+L7+L8+L9+L10+L11+L12+L13</f>
+        <v/>
+      </c>
+      <c r="M16" s="19" t="inlineStr">
+        <is>
+          <t>Required lines only; the optional lenses are below. Link 1 prices seen 2026-10-17, before shipping and tax. PCB not included: get a JLCPCB quote.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="K17" s="17" t="inlineStr">
+        <is>
           <t>Per-board share</t>
         </is>
       </c>
-      <c r="L16" s="18">
-        <f>C2/K2*J2+C3/K3*J3+C4/K4*J4+C5/K5*J5+C6/K6*J6+C7/K7*J7+C8/K8*J8+C9/K9*J9+C10/K10*J10+C11/K11*J11+C12/K12*J12</f>
+      <c r="L17" s="18">
+        <f>C2/K2*J2+C3/K3*J3+C6/K6*J6+C7/K7*J7+C8/K8*J8+C9/K9*J9+C10/K10*J10+C11/K11*J11+C12/K12*J12+C13/K13*J13</f>
         <v/>
       </c>
-      <c r="M16" s="19" t="inlineStr">
+      <c r="M17" s="19" t="inlineStr">
         <is>
           <t>Each pack pro-rated over the boards it covers.</t>
         </is>
       </c>
     </row>
+    <row r="18">
+      <c r="K18" s="20" t="inlineStr">
+        <is>
+          <t>Option: glass lenses, per board</t>
+        </is>
+      </c>
+      <c r="L18" s="21">
+        <f>L4</f>
+        <v/>
+      </c>
+      <c r="M18" s="19" t="inlineStr">
+        <is>
+          <t>Five watch crystals, one per display.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="K19" s="20" t="inlineStr">
+        <is>
+          <t>Option: acrylic lenses, per board</t>
+        </is>
+      </c>
+      <c r="L19" s="21" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="M19" s="19" t="inlineStr">
+        <is>
+          <t>Laser-cut in-house; price not set yet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="K20" s="20" t="inlineStr">
+        <is>
+          <t>Option: S3 Plus instead of S3, per board</t>
+        </is>
+      </c>
+      <c r="L20" s="21">
+        <f>7.9-J2</f>
+        <v/>
+      </c>
+      <c r="M20" s="19" t="inlineStr">
+        <is>
+          <t>The Plus ($7.90 on Seeed, seen 2026-10-17) REPLACES U2; only one XIAO goes on a board.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M13"/>
+  <autoFilter ref="A1:M14"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I2" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H3" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I3" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H4" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H5" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I5" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H6" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I6" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H7" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I7" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H8" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I8" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H9" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I9" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H10" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I10" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H11" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I11" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H12" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I12" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H13" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I13" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H6" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I6" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H7" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I7" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H8" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I8" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H9" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I9" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H10" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I10" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H11" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I11" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H12" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I12" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H13" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I13" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H14" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I14" r:id="rId23"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
